--- a/Outcome/Appendix/Joinpoint_APC_results.xlsx
+++ b/Outcome/Appendix/Joinpoint_APC_results.xlsx
@@ -32,49 +32,49 @@
     <t xml:space="preserve">P_value_Label</t>
   </si>
   <si>
-    <t xml:space="preserve">2008/01~2015/02</t>
+    <t xml:space="preserve">2008/01~2019/10</t>
   </si>
   <si>
     <t xml:space="preserve">Incidence</t>
   </si>
   <si>
+    <t xml:space="preserve">***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019/11~2021/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/06~2024/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008/01~2011/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortality</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">2015/03~2019/07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019/08~2021/05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021/06~2024/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008/01~2011/10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mortality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2011/11~2021/06</t>
+    <t xml:space="preserve">2011/10~2021/06</t>
   </si>
   <si>
     <t xml:space="preserve">2021/07~2024/12</t>
   </si>
   <si>
-    <t xml:space="preserve">2008/01~2013/01</t>
+    <t xml:space="preserve">2008/01~2012/11</t>
   </si>
   <si>
     <t xml:space="preserve">CFR</t>
   </si>
   <si>
-    <t xml:space="preserve">2013/02~2018/08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018/09~2024/12</t>
+    <t xml:space="preserve">2012/12~2018/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018/10~2024/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**</t>
   </si>
 </sst>
 </file>
@@ -431,13 +431,13 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.41</v>
+        <v>4.27</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.56</v>
+        <v>2.68</v>
       </c>
       <c r="E2" t="n">
-        <v>2.84</v>
+        <v>5.88</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -451,73 +451,73 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>13.3</v>
+        <v>-50.62</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4</v>
+        <v>-63.05</v>
       </c>
       <c r="E3" t="n">
-        <v>20.64</v>
+        <v>-34.01</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>-54.48</v>
+        <v>78.43</v>
       </c>
       <c r="D4" t="n">
-        <v>-65.83</v>
+        <v>62.22</v>
       </c>
       <c r="E4" t="n">
-        <v>-39.37</v>
+        <v>96.25</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
       <c r="C5" t="n">
-        <v>80.81</v>
+        <v>11.93</v>
       </c>
       <c r="D5" t="n">
-        <v>65.1</v>
+        <v>-3.43</v>
       </c>
       <c r="E5" t="n">
-        <v>98.02</v>
+        <v>29.74</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>11.91</v>
+        <v>-15.08</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.09</v>
+        <v>-16.57</v>
       </c>
       <c r="E6" t="n">
-        <v>29.23</v>
+        <v>-13.55</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -528,19 +528,19 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>-15.1</v>
+        <v>58.25</v>
       </c>
       <c r="D7" t="n">
-        <v>-16.65</v>
+        <v>42.94</v>
       </c>
       <c r="E7" t="n">
-        <v>-13.52</v>
+        <v>75.21</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -548,36 +548,36 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>59.13</v>
+        <v>-0.55</v>
       </c>
       <c r="D8" t="n">
-        <v>43.42</v>
+        <v>-8.14</v>
       </c>
       <c r="E8" t="n">
-        <v>76.55</v>
+        <v>7.67</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
       <c r="C9" t="n">
-        <v>-3.3</v>
+        <v>-19.58</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.7</v>
+        <v>-22.8</v>
       </c>
       <c r="E9" t="n">
-        <v>1.31</v>
+        <v>-16.23</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -588,39 +588,19 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>-40.77</v>
+        <v>8.67</v>
       </c>
       <c r="D10" t="n">
-        <v>-52.26</v>
+        <v>3.39</v>
       </c>
       <c r="E10" t="n">
-        <v>-26.51</v>
+        <v>14.21</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="F11" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Outcome/Appendix/Joinpoint_APC_results.xlsx
+++ b/Outcome/Appendix/Joinpoint_APC_results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">DateRange</t>
   </si>
@@ -47,31 +47,34 @@
     <t xml:space="preserve">2021/06~2024/12</t>
   </si>
   <si>
-    <t xml:space="preserve">2008/01~2011/09</t>
+    <t xml:space="preserve">2008/01~2011/12</t>
   </si>
   <si>
     <t xml:space="preserve">Mortality</t>
   </si>
   <si>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012/01~2021/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/07~2024/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008/01~2012/08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFR</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">2011/10~2021/06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021/07~2024/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008/01~2012/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2012/12~2018/09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018/10~2024/12</t>
+    <t xml:space="preserve">2012/09~2018/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018/12~2024/12</t>
   </si>
   <si>
     <t xml:space="preserve">**</t>
@@ -431,13 +434,13 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>4.27</v>
+        <v>4.98</v>
       </c>
       <c r="D2" t="n">
-        <v>2.68</v>
+        <v>3.34</v>
       </c>
       <c r="E2" t="n">
-        <v>5.88</v>
+        <v>6.65</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -451,13 +454,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>-50.62</v>
+        <v>-52.58</v>
       </c>
       <c r="D3" t="n">
-        <v>-63.05</v>
+        <v>-64.83</v>
       </c>
       <c r="E3" t="n">
-        <v>-34.01</v>
+        <v>-36.06</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -471,13 +474,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>78.43</v>
+        <v>83.19</v>
       </c>
       <c r="D4" t="n">
-        <v>62.22</v>
+        <v>66.07</v>
       </c>
       <c r="E4" t="n">
-        <v>96.25</v>
+        <v>102.07</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -491,13 +494,13 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>11.93</v>
+        <v>17.29</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.43</v>
+        <v>1.75</v>
       </c>
       <c r="E5" t="n">
-        <v>29.74</v>
+        <v>35.2</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -511,13 +514,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>-15.08</v>
+        <v>-15.03</v>
       </c>
       <c r="D6" t="n">
-        <v>-16.57</v>
+        <v>-16.54</v>
       </c>
       <c r="E6" t="n">
-        <v>-13.55</v>
+        <v>-13.49</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -531,13 +534,13 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>58.25</v>
+        <v>60.25</v>
       </c>
       <c r="D7" t="n">
-        <v>42.94</v>
+        <v>44.06</v>
       </c>
       <c r="E7" t="n">
-        <v>75.21</v>
+        <v>78.26</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -551,33 +554,33 @@
         <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.55</v>
+        <v>2.28</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.14</v>
+        <v>-6.01</v>
       </c>
       <c r="E8" t="n">
-        <v>7.67</v>
+        <v>11.3</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-19.58</v>
+        <v>-19.91</v>
       </c>
       <c r="D9" t="n">
-        <v>-22.8</v>
+        <v>-23.11</v>
       </c>
       <c r="E9" t="n">
-        <v>-16.23</v>
+        <v>-16.58</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -585,22 +588,22 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>8.67</v>
+        <v>8.99</v>
       </c>
       <c r="D10" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="E10" t="n">
-        <v>14.21</v>
+        <v>14.87</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Outcome/Appendix/Joinpoint_APC_results.xlsx
+++ b/Outcome/Appendix/Joinpoint_APC_results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t xml:space="preserve">DateRange</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">Mortality</t>
   </si>
   <si>
-    <t xml:space="preserve">*</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">2012/01~2021/06</t>
@@ -68,16 +68,10 @@
     <t xml:space="preserve">CFR</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">2012/09~2018/11</t>
   </si>
   <si>
     <t xml:space="preserve">2018/12~2024/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**</t>
   </si>
 </sst>
 </file>
@@ -434,13 +428,13 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>4.98</v>
+        <v>4.93</v>
       </c>
       <c r="D2" t="n">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="E2" t="n">
-        <v>6.65</v>
+        <v>6.59</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -454,13 +448,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>-52.58</v>
+        <v>-52.48</v>
       </c>
       <c r="D3" t="n">
-        <v>-64.83</v>
+        <v>-64.74</v>
       </c>
       <c r="E3" t="n">
-        <v>-36.06</v>
+        <v>-35.96</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -474,13 +468,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>83.19</v>
+        <v>82.84</v>
       </c>
       <c r="D4" t="n">
-        <v>66.07</v>
+        <v>65.78</v>
       </c>
       <c r="E4" t="n">
-        <v>102.07</v>
+        <v>101.66</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -494,13 +488,13 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>17.29</v>
+        <v>12.11</v>
       </c>
       <c r="D5" t="n">
-        <v>1.75</v>
+        <v>-0.55</v>
       </c>
       <c r="E5" t="n">
-        <v>35.2</v>
+        <v>26.38</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -514,13 +508,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>-15.03</v>
+        <v>-15.26</v>
       </c>
       <c r="D6" t="n">
-        <v>-16.54</v>
+        <v>-16.86</v>
       </c>
       <c r="E6" t="n">
-        <v>-13.49</v>
+        <v>-13.63</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -534,13 +528,13 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>60.25</v>
+        <v>60.83</v>
       </c>
       <c r="D7" t="n">
-        <v>44.06</v>
+        <v>45.13</v>
       </c>
       <c r="E7" t="n">
-        <v>78.26</v>
+        <v>78.23</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -554,33 +548,33 @@
         <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>2.28</v>
+        <v>-2.78</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.01</v>
+        <v>-7.27</v>
       </c>
       <c r="E8" t="n">
-        <v>11.3</v>
+        <v>1.93</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-19.91</v>
+        <v>-39.54</v>
       </c>
       <c r="D9" t="n">
-        <v>-23.11</v>
+        <v>-50.87</v>
       </c>
       <c r="E9" t="n">
-        <v>-16.58</v>
+        <v>-25.59</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -588,22 +582,22 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>8.99</v>
+        <v>2.05</v>
       </c>
       <c r="D10" t="n">
-        <v>3.41</v>
+        <v>-0.99</v>
       </c>
       <c r="E10" t="n">
-        <v>14.87</v>
+        <v>5.19</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Outcome/Appendix/Joinpoint_APC_results.xlsx
+++ b/Outcome/Appendix/Joinpoint_APC_results.xlsx
@@ -41,37 +41,37 @@
     <t xml:space="preserve">***</t>
   </si>
   <si>
-    <t xml:space="preserve">2019/11~2021/05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021/06~2024/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008/01~2011/12</t>
+    <t xml:space="preserve">2019/11~2021/03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/04~2025/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008/01~2012/01</t>
   </si>
   <si>
     <t xml:space="preserve">Mortality</t>
   </si>
   <si>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012/02~2021/03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008/01~2013/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFR</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">2012/01~2021/06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021/07~2024/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008/01~2012/08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2012/09~2018/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018/12~2024/12</t>
+    <t xml:space="preserve">2013/11~2016/08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016/09~2025/12</t>
   </si>
 </sst>
 </file>
@@ -428,13 +428,13 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>4.93</v>
+        <v>4.77</v>
       </c>
       <c r="D2" t="n">
-        <v>3.29</v>
+        <v>2.82</v>
       </c>
       <c r="E2" t="n">
-        <v>6.59</v>
+        <v>6.77</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -448,13 +448,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>-52.48</v>
+        <v>-49.88</v>
       </c>
       <c r="D3" t="n">
-        <v>-64.74</v>
+        <v>-65.92</v>
       </c>
       <c r="E3" t="n">
-        <v>-35.96</v>
+        <v>-26.28</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -468,13 +468,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>82.84</v>
+        <v>60.65</v>
       </c>
       <c r="D4" t="n">
-        <v>65.78</v>
+        <v>48.56</v>
       </c>
       <c r="E4" t="n">
-        <v>101.66</v>
+        <v>73.72</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -488,13 +488,13 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>12.11</v>
+        <v>17.29</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.55</v>
+        <v>0.21</v>
       </c>
       <c r="E5" t="n">
-        <v>26.38</v>
+        <v>37.29</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -508,13 +508,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>-15.26</v>
+        <v>-15.22</v>
       </c>
       <c r="D6" t="n">
-        <v>-16.86</v>
+        <v>-16.9</v>
       </c>
       <c r="E6" t="n">
-        <v>-13.63</v>
+        <v>-13.52</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -522,19 +522,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>60.83</v>
+        <v>40.64</v>
       </c>
       <c r="D7" t="n">
-        <v>45.13</v>
+        <v>31.63</v>
       </c>
       <c r="E7" t="n">
-        <v>78.23</v>
+        <v>50.26</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -542,22 +542,22 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="F8" t="s">
         <v>17</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-2.78</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-7.27</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -565,16 +565,16 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-39.54</v>
+        <v>-40.72</v>
       </c>
       <c r="D9" t="n">
-        <v>-50.87</v>
+        <v>-52.61</v>
       </c>
       <c r="E9" t="n">
-        <v>-25.59</v>
+        <v>-25.83</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -585,19 +585,19 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="F10" t="s">
         <v>17</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="E10" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Outcome/Appendix/Joinpoint_APC_results.xlsx
+++ b/Outcome/Appendix/Joinpoint_APC_results.xlsx
@@ -428,7 +428,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="D2" t="n">
         <v>2.82</v>
@@ -448,13 +448,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>-49.88</v>
+        <v>-49.74</v>
       </c>
       <c r="D3" t="n">
-        <v>-65.92</v>
+        <v>-65.83</v>
       </c>
       <c r="E3" t="n">
-        <v>-26.28</v>
+        <v>-26.08</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -468,13 +468,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>60.65</v>
+        <v>60.62</v>
       </c>
       <c r="D4" t="n">
-        <v>48.56</v>
+        <v>48.53</v>
       </c>
       <c r="E4" t="n">
-        <v>73.72</v>
+        <v>73.69</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -488,13 +488,13 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>17.29</v>
+        <v>17.28</v>
       </c>
       <c r="D5" t="n">
-        <v>0.21</v>
+        <v>0.91</v>
       </c>
       <c r="E5" t="n">
-        <v>37.29</v>
+        <v>36.31</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -511,7 +511,7 @@
         <v>-15.22</v>
       </c>
       <c r="D6" t="n">
-        <v>-16.9</v>
+        <v>-16.89</v>
       </c>
       <c r="E6" t="n">
         <v>-13.52</v>
@@ -528,13 +528,13 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>40.64</v>
+        <v>40.66</v>
       </c>
       <c r="D7" t="n">
-        <v>31.63</v>
+        <v>31.41</v>
       </c>
       <c r="E7" t="n">
-        <v>50.26</v>
+        <v>50.55</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>

--- a/Outcome/Appendix/Joinpoint_APC_results.xlsx
+++ b/Outcome/Appendix/Joinpoint_APC_results.xlsx
@@ -59,7 +59,7 @@
     <t xml:space="preserve">2012/02~2021/03</t>
   </si>
   <si>
-    <t xml:space="preserve">2008/01~2013/10</t>
+    <t xml:space="preserve">2008/01~2013/09</t>
   </si>
   <si>
     <t xml:space="preserve">CFR</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">2013/11~2016/08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016/09~2025/12</t>
+    <t xml:space="preserve">2013/10~2016/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016/08~2025/12</t>
   </si>
 </sst>
 </file>
@@ -428,13 +428,13 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>4.78</v>
+        <v>4.77</v>
       </c>
       <c r="D2" t="n">
-        <v>2.82</v>
+        <v>3.07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.77</v>
+        <v>6.5</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -448,13 +448,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>-49.74</v>
+        <v>-50.77</v>
       </c>
       <c r="D3" t="n">
-        <v>-65.83</v>
+        <v>-64.77</v>
       </c>
       <c r="E3" t="n">
-        <v>-26.08</v>
+        <v>-31.19</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -468,13 +468,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>60.62</v>
+        <v>68.05</v>
       </c>
       <c r="D4" t="n">
-        <v>48.53</v>
+        <v>57.02</v>
       </c>
       <c r="E4" t="n">
-        <v>73.69</v>
+        <v>79.85</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -488,13 +488,13 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>17.28</v>
+        <v>17.29</v>
       </c>
       <c r="D5" t="n">
-        <v>0.91</v>
+        <v>1.26</v>
       </c>
       <c r="E5" t="n">
-        <v>36.31</v>
+        <v>35.86</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -508,13 +508,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>-15.22</v>
+        <v>-15.23</v>
       </c>
       <c r="D6" t="n">
-        <v>-16.89</v>
+        <v>-16.86</v>
       </c>
       <c r="E6" t="n">
-        <v>-13.52</v>
+        <v>-13.56</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -528,13 +528,13 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>40.66</v>
+        <v>41.8</v>
       </c>
       <c r="D7" t="n">
-        <v>31.41</v>
+        <v>32.68</v>
       </c>
       <c r="E7" t="n">
-        <v>50.55</v>
+        <v>51.55</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -548,13 +548,13 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.65</v>
+        <v>-2.69</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.24</v>
+        <v>-7.29</v>
       </c>
       <c r="E8" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
@@ -568,13 +568,13 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-40.72</v>
+        <v>-40.17</v>
       </c>
       <c r="D9" t="n">
-        <v>-52.61</v>
+        <v>-52.82</v>
       </c>
       <c r="E9" t="n">
-        <v>-25.83</v>
+        <v>-24.13</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -588,13 +588,13 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7</v>
+        <v>-0.15</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.87</v>
+        <v>-2.66</v>
       </c>
       <c r="E10" t="n">
-        <v>3.33</v>
+        <v>2.44</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>

--- a/Outcome/Appendix/Joinpoint_APC_results.xlsx
+++ b/Outcome/Appendix/Joinpoint_APC_results.xlsx
@@ -428,7 +428,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="D2" t="n">
         <v>3.07</v>
@@ -448,13 +448,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>-50.77</v>
+        <v>-50.75</v>
       </c>
       <c r="D3" t="n">
-        <v>-64.77</v>
+        <v>-64.76</v>
       </c>
       <c r="E3" t="n">
-        <v>-31.19</v>
+        <v>-31.17</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -468,13 +468,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>68.05</v>
+        <v>68.85</v>
       </c>
       <c r="D4" t="n">
-        <v>57.02</v>
+        <v>57.76</v>
       </c>
       <c r="E4" t="n">
-        <v>79.85</v>
+        <v>80.71</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -488,13 +488,13 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>17.29</v>
+        <v>17.3</v>
       </c>
       <c r="D5" t="n">
-        <v>1.26</v>
+        <v>0.59</v>
       </c>
       <c r="E5" t="n">
-        <v>35.86</v>
+        <v>36.78</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -511,10 +511,10 @@
         <v>-15.23</v>
       </c>
       <c r="D6" t="n">
-        <v>-16.86</v>
+        <v>-16.84</v>
       </c>
       <c r="E6" t="n">
-        <v>-13.56</v>
+        <v>-13.59</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -528,13 +528,13 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>41.8</v>
+        <v>42.19</v>
       </c>
       <c r="D7" t="n">
-        <v>32.68</v>
+        <v>33.06</v>
       </c>
       <c r="E7" t="n">
-        <v>51.55</v>
+        <v>51.94</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>-2.69</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.29</v>
+        <v>-7.3</v>
       </c>
       <c r="E8" t="n">
         <v>2.15</v>
@@ -568,13 +568,13 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-40.17</v>
+        <v>-40.14</v>
       </c>
       <c r="D9" t="n">
-        <v>-52.82</v>
+        <v>-52.81</v>
       </c>
       <c r="E9" t="n">
-        <v>-24.13</v>
+        <v>-24.06</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -588,13 +588,13 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.15</v>
+        <v>-0.18</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.66</v>
+        <v>-2.7</v>
       </c>
       <c r="E10" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>

--- a/Outcome/Appendix/Joinpoint_APC_results.xlsx
+++ b/Outcome/Appendix/Joinpoint_APC_results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve">DateRange</t>
   </si>
@@ -41,10 +41,10 @@
     <t xml:space="preserve">***</t>
   </si>
   <si>
-    <t xml:space="preserve">2019/11~2021/03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021/04~2025/12</t>
+    <t xml:space="preserve">2019/11~2021/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/06~2025/12</t>
   </si>
   <si>
     <t xml:space="preserve">2008/01~2012/01</t>
@@ -56,10 +56,13 @@
     <t xml:space="preserve">*</t>
   </si>
   <si>
-    <t xml:space="preserve">2012/02~2021/03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008/01~2013/09</t>
+    <t xml:space="preserve">2012/02~2021/04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/05~2025/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008/01~2013/10</t>
   </si>
   <si>
     <t xml:space="preserve">CFR</t>
@@ -68,7 +71,7 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">2013/10~2016/07</t>
+    <t xml:space="preserve">2013/11~2016/07</t>
   </si>
   <si>
     <t xml:space="preserve">2016/08~2025/12</t>
@@ -431,10 +434,10 @@
         <v>4.78</v>
       </c>
       <c r="D2" t="n">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5</v>
+        <v>6.47</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -451,10 +454,10 @@
         <v>-50.75</v>
       </c>
       <c r="D3" t="n">
-        <v>-64.76</v>
+        <v>-64.52</v>
       </c>
       <c r="E3" t="n">
-        <v>-31.17</v>
+        <v>-31.64</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -468,13 +471,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>68.85</v>
+        <v>71.71</v>
       </c>
       <c r="D4" t="n">
-        <v>57.76</v>
+        <v>60.67</v>
       </c>
       <c r="E4" t="n">
-        <v>80.71</v>
+        <v>83.52</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -488,13 +491,13 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>17.3</v>
+        <v>17.02</v>
       </c>
       <c r="D5" t="n">
-        <v>0.59</v>
+        <v>1.63</v>
       </c>
       <c r="E5" t="n">
-        <v>36.78</v>
+        <v>34.75</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -508,13 +511,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>-15.23</v>
+        <v>-15.12</v>
       </c>
       <c r="D6" t="n">
-        <v>-16.84</v>
+        <v>-16.65</v>
       </c>
       <c r="E6" t="n">
-        <v>-13.59</v>
+        <v>-13.55</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -522,19 +525,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>42.19</v>
+        <v>47.09</v>
       </c>
       <c r="D7" t="n">
-        <v>33.06</v>
+        <v>37.51</v>
       </c>
       <c r="E7" t="n">
-        <v>51.94</v>
+        <v>57.34</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -542,39 +545,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.69</v>
+        <v>-2.65</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.3</v>
+        <v>-7.25</v>
       </c>
       <c r="E8" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>-40.14</v>
+        <v>-40.27</v>
       </c>
       <c r="D9" t="n">
-        <v>-52.81</v>
+        <v>-52.25</v>
       </c>
       <c r="E9" t="n">
-        <v>-24.06</v>
+        <v>-25.28</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -582,22 +585,22 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.18</v>
+        <v>0.03</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7</v>
+        <v>-2.52</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
